--- a/docentes/Reyes Cruz Eder Yaveth - Estadisticos 20232.xlsx
+++ b/docentes/Reyes Cruz Eder Yaveth - Estadisticos 20232.xlsx
@@ -562,16 +562,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +588,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -650,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Reyes Cruz Eder Yaveth - Estadisticos 20232.xlsx
+++ b/docentes/Reyes Cruz Eder Yaveth - Estadisticos 20232.xlsx
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>96.88</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
